--- a/results/Int All Data 0.9/Rando_fi_explain.xlsx
+++ b/results/Int All Data 0.9/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001968357219641737</v>
+        <v>3.422395458673622e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>2.060693610272057e-05</v>
+        <v>0.0002812799114398578</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006428538288273611</v>
+        <v>7.291948078913535e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.708715402564146e-06</v>
+        <v>0.0008585028178704632</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0001134238692144984</v>
+        <v>2.871952248089672e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0003570750185820371</v>
+        <v>0.00214782979550297</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0006007291023067162</v>
+        <v>0.000806340077087394</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0003437313091250526</v>
+        <v>0.0001200121873357407</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0006306032648449543</v>
+        <v>0.0001300406076286831</v>
       </c>
       <c r="K3" t="n">
-        <v>9.092653261775664e-05</v>
+        <v>6.94249550020576e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.151447504770365e-05</v>
+        <v>-9.736088799847109e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0001845773292901076</v>
+        <v>9.183755894562331e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0003141135109618686</v>
+        <v>6.339140497058169e-07</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0005809721478560581</v>
+        <v>0.0004603697443720722</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0004987347700847212</v>
+        <v>5.930412327279421e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003202853116866409</v>
+        <v>0.001376635682425567</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0009955485035953128</v>
+        <v>0.0005277211558412877</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004956724003472834</v>
+        <v>-0.0002380992205255739</v>
       </c>
       <c r="T3" t="n">
-        <v>5.715825220455875e-06</v>
+        <v>0.0003538227437899088</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0001656524584850872</v>
+        <v>0.0003847129207937528</v>
       </c>
       <c r="V3" t="n">
-        <v>0.000689697908780087</v>
+        <v>-9.766609594833997e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0001692984239493922</v>
+        <v>0.0002509406371171319</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001751656312655052</v>
+        <v>0.0004502218973081451</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.0002029327548104698</v>
+        <v>0.0001982170423491381</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0006407335501739653</v>
+        <v>0.0001242180343135213</v>
       </c>
       <c r="AA3" t="n">
-        <v>-7.225615607940443e-05</v>
+        <v>-0.0004364455022053804</v>
       </c>
       <c r="AB3" t="n">
-        <v>-8.239116247498178e-06</v>
+        <v>0.0003244626387330829</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.000879665772978039</v>
+        <v>0.001770485718783556</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.006170251918073409</v>
+        <v>0.003840381651191251</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.01125595225683161</v>
+        <v>0.009737075490492525</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0001483326225905079</v>
+        <v>0.0001222869444231466</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0002867730425910264</v>
+        <v>0.0007183468412264803</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0005046369202438029</v>
+        <v>0.000698675650394025</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0002578267154366021</v>
+        <v>0.0007974710757328351</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.003119578336017948</v>
+        <v>0.001333487366191807</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01436873147663788</v>
+        <v>0.01511726758953534</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.415756893389128e-05</v>
+        <v>0.0006117931270316967</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.005950548781121523</v>
+        <v>0.005036767700695001</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.506817853709321e-05</v>
+        <v>0.0008544179051797231</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.002510312004244945</v>
+        <v>0.001462186351969095</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0003900459830797054</v>
+        <v>0.0003939425089350002</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.0003518337571485386</v>
+        <v>-0.0006139050647355871</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.008421547933269075</v>
+        <v>0.01001829660151319</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0003342969695579634</v>
+        <v>0.001095115105166078</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.001010952700076867</v>
+        <v>0.0004355016380100907</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0002385815861033325</v>
+        <v>-7.105959948615626e-05</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.0002014076039505219</v>
+        <v>7.306237857601762e-05</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.0002619519902558562</v>
+        <v>5.992427796310831e-06</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0002037766415560349</v>
+        <v>0.0001217844847277938</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.0002122317396589679</v>
+        <v>-0.0006847603848354211</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.0005688453138978954</v>
+        <v>0.0001924996017562852</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.0009472395063297877</v>
+        <v>0.0002340530246153171</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.001348323469070031</v>
+        <v>-0.0004887578188372888</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0002489794981033732</v>
+        <v>9.792025329785514e-05</v>
       </c>
       <c r="BD3" t="n">
-        <v>9.840624280941124e-05</v>
+        <v>0.0003231343820239874</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.002216748909443667</v>
+        <v>-0.0001834973176371124</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.0003350943247373684</v>
+        <v>-0.0008425542992096738</v>
       </c>
       <c r="BG3" t="n">
-        <v>-7.449519775088898e-05</v>
+        <v>0.0003416642694152994</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.192545351108808e-05</v>
+        <v>0.0001502416141348817</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.003375802583694594</v>
+        <v>0.001881435146204894</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.001290857790479848</v>
+        <v>0.0004162876887240951</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.000567027378663476</v>
+        <v>0.0002545199670964837</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0001861674462373786</v>
+        <v>8.515108017416169e-06</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.001344203219263045</v>
+        <v>0.001161982250320945</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.001515527185695561</v>
+        <v>0.0009259379566663728</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0003015317406531937</v>
+        <v>-2.048513928096351e-05</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.001222243345808749</v>
+        <v>0.0003024411877351119</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0.0003968662624512421</v>
+        <v>-0.0008839499298548216</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0002032892225795402</v>
+        <v>-1.960292924157781e-05</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0008621297169171015</v>
+        <v>-9.519838030183525e-05</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.00106848753806919</v>
+        <v>-0.0008501323131435822</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.0004895938126014342</v>
+        <v>-0.0005961300776785606</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.068947087119243e-05</v>
+        <v>-1.110223024625157e-18</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.001254095508704563</v>
+        <v>-0.0009939534572864328</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0005450098504121458</v>
+        <v>0.001600691191879432</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.002009426996182454</v>
+        <v>0.001210920751358316</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.0006320098821621601</v>
+        <v>0.0007650066603668183</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0.001158490530044226</v>
+        <v>-0.0004822647776481515</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.0002857485778761526</v>
+        <v>0.0003854839219878025</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.0005980133476170569</v>
+        <v>0.0005892958438814444</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.0002936151539073184</v>
+        <v>-0.000824484093836767</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.0003901265960891532</v>
+        <v>0.0004888785724704459</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0002240906617757555</v>
+        <v>-0.0008689142775658621</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0005066215123804263</v>
+        <v>0.0002531526677378137</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.0004662012922940295</v>
+        <v>-0.0005435402226826479</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-1.062178029047844e-05</v>
+        <v>1.068947087119132e-05</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0005496341068700261</v>
+        <v>-5.432247616160234e-05</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.0002185214065131292</v>
+        <v>0.0005974514240085104</v>
       </c>
       <c r="CM3" t="n">
-        <v>4.462704452771859e-05</v>
+        <v>0.0001603459238111549</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.0001252472594713494</v>
+        <v>0.0003048339987829973</v>
       </c>
       <c r="CO3" t="n">
-        <v>-5.892151763847698e-06</v>
+        <v>8.005915847405731e-05</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.553571118940167e-05</v>
+        <v>-4.167971846567031e-05</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.000104596896983391</v>
+        <v>-0.0001219219293297158</v>
       </c>
       <c r="CR3" t="n">
-        <v>-3.586118509194091e-05</v>
+        <v>0.001145985978232884</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.0003025667148621802</v>
+        <v>1.443715291706894e-06</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.0009575660951668773</v>
+        <v>-0.0002954548840105686</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.105492437047273e-05</v>
+        <v>-0.0001082317097159036</v>
       </c>
       <c r="CV3" t="n">
-        <v>5.407276817409711e-05</v>
+        <v>-9.086050240512456e-05</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.0002590651937792843</v>
+        <v>0.0007717517426717414</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0.001937690081057662</v>
+        <v>0.0001858643499122604</v>
       </c>
       <c r="CZ3" t="n">
-        <v>4.798958410379472e-05</v>
+        <v>0</v>
       </c>
       <c r="DA3" t="n">
-        <v>7.220976890000007e-06</v>
+        <v>1.695010900719218e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0.0001725834658351188</v>
+        <v>0.0001813651652089421</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.0002341876574339452</v>
+        <v>-8.154418729241941e-05</v>
       </c>
       <c r="DD3" t="n">
-        <v>-0.0001091632531083719</v>
+        <v>0.0001028036381924846</v>
       </c>
       <c r="DE3" t="n">
-        <v>6.39146711144756e-05</v>
+        <v>1.92742148301217e-05</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.0004964567658711161</v>
+        <v>0.0001938049292106825</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.0004182532994508048</v>
+        <v>4.535535272504389e-05</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.001751510272658305</v>
+        <v>-0.001257838859425202</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.0006969493706465157</v>
+        <v>-5.452484922724544e-05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.0003073221791109504</v>
+        <v>6.399861034177557e-05</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0.0002243620987837924</v>
+        <v>0.0004354092181228264</v>
       </c>
       <c r="DL3" t="n">
-        <v>5.277044854881119e-06</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.0002134317259025786</v>
+        <v>0.000342510560117647</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.0006347099667583222</v>
+        <v>-0.0003966082103550716</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.0008185418469176253</v>
+        <v>-0.0001391748160367346</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.0005656697514047494</v>
+        <v>-0.0001531164276830655</v>
       </c>
       <c r="DQ3" t="n">
-        <v>5.344735435596215e-06</v>
+        <v>-6.465036598540252e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.0001016491000013342</v>
+        <v>0.0001177784546654526</v>
       </c>
       <c r="DS3" t="n">
-        <v>-7.896289862548978e-05</v>
+        <v>-0.0002517258708839188</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.0006323690582810859</v>
+        <v>0.0005093931283726728</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0.0004545081551690689</v>
+        <v>-0.0009172173252716964</v>
       </c>
       <c r="DV3" t="n">
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-2.192982456140413e-05</v>
+        <v>-5.447857966690894e-05</v>
       </c>
       <c r="DX3" t="n">
-        <v>-5.68870099721952e-05</v>
+        <v>-0.0002002394800901097</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.001628470840678268</v>
+        <v>-0.002318781445949029</v>
       </c>
       <c r="DZ3" t="n">
-        <v>1.377207047548178e-07</v>
+        <v>2.241154591985372e-06</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.0001689358909996996</v>
+        <v>-8.214928591445683e-06</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.0001982105377136878</v>
+        <v>-0.0006901152466662808</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.0002232284908746373</v>
+        <v>0.000778584552236523</v>
       </c>
       <c r="ED3" t="n">
-        <v>-1.267589314517759e-05</v>
+        <v>5.63485254452678e-05</v>
       </c>
       <c r="EE3" t="n">
-        <v>4.824033962511965e-05</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.0001541458364343895</v>
+        <v>2.703147804298254e-05</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.0003426662504357514</v>
+        <v>-0.0002131802021974072</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.00010561244493135</v>
+        <v>0.0001722369661592393</v>
       </c>
       <c r="EI3" t="n">
-        <v>-2.376326075038571e-05</v>
+        <v>-0.0001864508027981515</v>
       </c>
       <c r="EJ3" t="n">
-        <v>9.019505750355593e-05</v>
+        <v>-0.0001566994127213506</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.000253360106008651</v>
+        <v>-1.017145432702926e-05</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
       </c>
       <c r="EM3" t="n">
-        <v>5.801880205156262e-05</v>
+        <v>1.118730598759217e-07</v>
       </c>
       <c r="EN3" t="n">
-        <v>9.475088806233934e-05</v>
+        <v>-4.789954717821621e-05</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-7.76276070221238e-07</v>
+        <v>-0.0001068947087119243</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.0003271731934736899</v>
+        <v>-7.48939866790521e-05</v>
       </c>
       <c r="ER3" t="n">
-        <v>-1.068947087119243e-05</v>
+        <v>0</v>
       </c>
       <c r="ES3" t="n">
         <v>0</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.0001059701058755547</v>
+        <v>-2.144908746590346e-05</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.0001206912815837491</v>
+        <v>-5.2445972531594e-05</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.0003202349705593376</v>
+        <v>0.000115211337224157</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0.0007580848469379642</v>
+        <v>-5.80181425958215e-05</v>
       </c>
       <c r="EX3" t="n">
-        <v>1.819264691340414e-05</v>
+        <v>5.844834802123499e-05</v>
       </c>
       <c r="EY3" t="n">
-        <v>2.104555255324048e-05</v>
+        <v>2.314134039443914e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004368620426299168</v>
+        <v>0.001284221912386192</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0008535502814105194</v>
+        <v>0.001130691926116238</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001174693598280736</v>
+        <v>0.0006663868427518658</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0009983000297369012</v>
+        <v>0.001491510272082679</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0005078723220171031</v>
+        <v>0.0001543615145218989</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004206560986126585</v>
+        <v>0.004612743177498753</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002075608003168306</v>
+        <v>0.002767898034077664</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00229772643756651</v>
+        <v>0.0009178871625047714</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003032389638624567</v>
+        <v>0.001210533040060832</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006289958839609763</v>
+        <v>0.0003549756507204291</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005996427297107781</v>
+        <v>0.0001487078060223186</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00096359522239064</v>
+        <v>0.001033332510482356</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003218018332838103</v>
+        <v>0.002698283366922256</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001593523404510419</v>
+        <v>0.0008829882771970323</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003287115559440336</v>
+        <v>0.0008943482597057341</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003872774880794472</v>
+        <v>0.001849901236272787</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001955077909922416</v>
+        <v>0.001953485369793958</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0027900950216209</v>
+        <v>0.001815721801906333</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001210734876198647</v>
+        <v>0.0006303283646880452</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001163137263406069</v>
+        <v>0.001706473090429105</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001133593572229455</v>
+        <v>0.0006028721138468345</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0009565290983558313</v>
+        <v>0.001417920625880085</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001589222260874426</v>
+        <v>0.001229838275668552</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0003492151283400445</v>
+        <v>0.0006999450871387375</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002827656101750032</v>
+        <v>0.001234870438661812</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001860546559573405</v>
+        <v>0.001273191228237012</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0003426573142238448</v>
+        <v>0.0008023726402290177</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.00407061347342059</v>
+        <v>0.005203436703387362</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.01118540425117539</v>
+        <v>0.008204544366570754</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0136440097224034</v>
+        <v>0.01219276211743212</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.002452723189705875</v>
+        <v>0.003417311040074651</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001870162488484237</v>
+        <v>0.001332504803899799</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.00108657085436072</v>
+        <v>0.0009608346046945412</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.0009140671668062306</v>
+        <v>0.00166570690618527</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.006095635194726902</v>
+        <v>0.003919093953373346</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.014456030596059</v>
+        <v>0.01510807013431266</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001933285575484721</v>
+        <v>0.00208173830882465</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.01294155065817722</v>
+        <v>0.01013297374817035</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.001966932385739674</v>
+        <v>0.001893310011176896</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.004012988969746631</v>
+        <v>0.003199293709716638</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0007598410022718162</v>
+        <v>0.0006272873761412629</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.001577546245967796</v>
+        <v>0.001955496274662332</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.01378717956366619</v>
+        <v>0.01220154938371596</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0009853102083091881</v>
+        <v>0.00210759837086026</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.002095370527269387</v>
+        <v>0.0008624992473900452</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.001618159756539811</v>
+        <v>0.0007383257400428485</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.001817210495081937</v>
+        <v>0.001341212334095158</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.00491817044533178</v>
+        <v>0.004723980992691845</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0004754975957349885</v>
+        <v>0.0002655349605516964</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.001202595444740805</v>
+        <v>0.003696171867100387</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.001723099848525274</v>
+        <v>0.0008324684309201165</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.00357814104771779</v>
+        <v>0.004365875256246669</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.004267732329062077</v>
+        <v>0.005248079297598459</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0005561006728558013</v>
+        <v>0.0003227824374633702</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0001984658687651275</v>
+        <v>0.0006457980522652335</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.004495041235266667</v>
+        <v>0.001313150875499279</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.004348827545954522</v>
+        <v>0.008152049300147306</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.0004379222140665285</v>
+        <v>0.001363534675779888</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001690142279548045</v>
+        <v>0.000296017522830818</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.006259883608477138</v>
+        <v>0.003062429094275784</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.003377412086223146</v>
+        <v>0.003132215649302174</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.00172342387593195</v>
+        <v>0.0007821738597766254</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0005800845684972136</v>
+        <v>0.0005006418954500793</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.005982510780864934</v>
+        <v>0.004903110668436013</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.002689321983993367</v>
+        <v>0.003554287871692715</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.001198949657230677</v>
+        <v>0.000783378516368274</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.004494121227014102</v>
+        <v>0.0009882434470163313</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.002368175442891914</v>
+        <v>0.004082864642413401</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.001032945767728307</v>
+        <v>0.000484700900599736</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.002478446372116752</v>
+        <v>0.0003783156723319557</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.004460901401244869</v>
+        <v>0.002063839414745836</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.001526102086528317</v>
+        <v>0.002279035986355199</v>
       </c>
       <c r="BW4" t="n">
-        <v>3.380307493499244e-05</v>
+        <v>3.510833468576701e-18</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.002896841895943826</v>
+        <v>0.00287628012244641</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.004468463915226334</v>
+        <v>0.004280785543903607</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.004908438739961134</v>
+        <v>0.004495706616089575</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.001660078374596077</v>
+        <v>0.001473893452574231</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.002800940687333082</v>
+        <v>0.001613758078395327</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.002201888394085442</v>
+        <v>0.002128676872386612</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.003503426241020503</v>
+        <v>0.002122229826492589</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.001444849769279748</v>
+        <v>0.002894577440310496</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001009694303490355</v>
+        <v>0.002056459961047049</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.002594364435613537</v>
+        <v>0.002756339741851036</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001246869059853127</v>
+        <v>0.0004619612435357678</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.001710092589894445</v>
+        <v>0.003630486528711646</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.239324740060847e-05</v>
+        <v>5.520019021852196e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.001231768598771952</v>
+        <v>0.0005921655545135883</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.00129681153075458</v>
+        <v>0.00156219427435744</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.000731099223796538</v>
+        <v>0.0002425778175928054</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.000599055798338225</v>
+        <v>0.0006700292210613895</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0007278403225292673</v>
+        <v>0.0002353581325668469</v>
       </c>
       <c r="CP4" t="n">
-        <v>6.624322454822091e-05</v>
+        <v>0.0001483502175580471</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.0008111212057196933</v>
+        <v>0.0003870553650835302</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.001860797532438999</v>
+        <v>0.003167737476631385</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.002341628058064981</v>
+        <v>0.00247021237505081</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.001972017685987932</v>
+        <v>0.001263043629146309</v>
       </c>
       <c r="CU4" t="n">
-        <v>4.136753749649852e-05</v>
+        <v>0.0004249686677411076</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.00015118488325773</v>
+        <v>0.0002225903894407118</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.002367487310174629</v>
+        <v>0.003244621760704088</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.00253204055065358</v>
+        <v>0.001311892893119275</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.000152467518161357</v>
+        <v>0</v>
       </c>
       <c r="DA4" t="n">
-        <v>6.910818216454251e-05</v>
+        <v>9.715283170941378e-05</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0005460065858598256</v>
+        <v>0.0003909982560590003</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.001065294828339897</v>
+        <v>0.0005170071944019603</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0005343539818822633</v>
+        <v>0.0002972673947860377</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.0007808158787500331</v>
+        <v>0.0003763613988437029</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.00128353456737444</v>
+        <v>0.0006807572035268346</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.0008575858409885754</v>
+        <v>0.0006828858337606133</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.004934061016410646</v>
+        <v>0.00402313617316881</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0009795525967299047</v>
+        <v>0.0005236551673045081</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0004227596075320419</v>
+        <v>0.0001834730662322107</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.00125611046814453</v>
+        <v>0.0009660082297987951</v>
       </c>
       <c r="DL4" t="n">
-        <v>1.668748105629705e-05</v>
+        <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0008770583916190998</v>
+        <v>0.001196269231502243</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.001992405243511951</v>
+        <v>0.002033640523721145</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.002437407961519942</v>
+        <v>0.002526055720668476</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.00457648249603816</v>
+        <v>0.001232471048854336</v>
       </c>
       <c r="DQ4" t="n">
-        <v>1.690153746749622e-05</v>
+        <v>0.0001667225984882644</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0002801169036041207</v>
+        <v>0.0002520077432702023</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0002125140767017693</v>
+        <v>0.0007588645359351215</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.003431081726142631</v>
+        <v>0.001717647440463042</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.002794816506993835</v>
+        <v>0.00353234397872064</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>6.934819430194013e-05</v>
+        <v>0.0001620045129246248</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0005575748302561381</v>
+        <v>0.0003399837397614272</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.004196775916068827</v>
+        <v>0.004720404507737109</v>
       </c>
       <c r="DZ4" t="n">
-        <v>2.55215868341856e-05</v>
+        <v>8.005069085510258e-05</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.0005072350222992767</v>
+        <v>0.0006908404890240917</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.003349927471397938</v>
+        <v>0.002873401734474256</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.001153320569152106</v>
+        <v>0.001508074659759773</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0002573247628696296</v>
+        <v>0.0002534100301819407</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0001343949771181627</v>
+        <v>0</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0005301301305617111</v>
+        <v>0.0005234185749170219</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0008698596897925275</v>
+        <v>0.0003923001227628007</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0004854172725857702</v>
+        <v>0.0006234101707670485</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.0004216100949479782</v>
+        <v>0.0004057714470259399</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0009616545169844186</v>
+        <v>0.0002837723154068686</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.001205849666758784</v>
+        <v>0.0001293213754629455</v>
       </c>
       <c r="EL4" t="n">
         <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0001831459171106815</v>
+        <v>2.493275265847244e-05</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0002222131925215988</v>
+        <v>0.0001477117894647331</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>4.373404126899068e-05</v>
+        <v>0.0003380307493499245</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.0007794649128592602</v>
+        <v>0.0002559151459967225</v>
       </c>
       <c r="ER4" t="n">
-        <v>3.380307493499244e-05</v>
+        <v>0</v>
       </c>
       <c r="ES4" t="n">
         <v>0</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.000964072816860398</v>
+        <v>0.000190738036873716</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.0008269699238367748</v>
+        <v>0.0004904183514427687</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.000879591993162175</v>
+        <v>0.0003289235480978175</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.001864564699341638</v>
+        <v>0.001276264458685739</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0008443547378244731</v>
+        <v>0.0002660097895781117</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.000173799897077684</v>
+        <v>0.0001726470296056333</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.009246392303580941</v>
+        <v>-0.003046499198289643</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.001465201465201393</v>
+        <v>-0.0003741314804916574</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.000657894736842124</v>
+        <v>-0.001603420630678754</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.001443078567610867</v>
+        <v>-0.0005756148613291323</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.001465201465201371</v>
+        <v>-0.0002110817941952448</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.006948156066274702</v>
+        <v>-0.001319261213720369</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.004716417910447778</v>
+        <v>-0.0008895866038722722</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.006253340459647228</v>
+        <v>-0.001496525921966829</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.007001603420630664</v>
+        <v>-0.002244788882950244</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.001014925373134357</v>
+        <v>-0.000361445783132508</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.001603420630678765</v>
+        <v>-0.0004275788348476195</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.00261892036344199</v>
+        <v>-0.0008895866038722943</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.006894708711918751</v>
+        <v>-0.006467129877071043</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0015478164731896</v>
+        <v>-0.0001046572475143503</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.008925708177445191</v>
+        <v>-0.001122394441475194</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0005482456140351033</v>
+        <v>-0.001319261213720357</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.004115446285408853</v>
+        <v>-0.0004749340369393118</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.006520577231427027</v>
+        <v>-0.004703367183324381</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.001927710843373498</v>
+        <v>-0.0003166226912928782</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.002985074626865702</v>
+        <v>-0.001726844583987419</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.000694815606627508</v>
+        <v>-0.001389631213254972</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.00126649076517158</v>
+        <v>-0.001867469879518036</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.001084337349397635</v>
+        <v>-0.002298236237306284</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.0008017103153393768</v>
+        <v>-0.0005232862375719293</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.003701492537313456</v>
+        <v>-0.001603420630678754</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.004119402985074638</v>
+        <v>-0.00358097274184932</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0005373134328358175</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.003588390501319316</v>
+        <v>-0.004749340369393162</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.005024051309460198</v>
+        <v>-0.00753607696419023</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.0145074626865672</v>
+        <v>-0.006328358208955232</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.002925373134328391</v>
+        <v>-0.006894708711918806</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.001656867985034738</v>
+        <v>-0.000328947368421062</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.0009823182711198087</v>
+        <v>-0.0001583113456464336</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.0007858546168958314</v>
+        <v>-0.001308215593929885</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.009014925373134374</v>
+        <v>-0.006985074626865673</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.004649919828968485</v>
+        <v>-0.008284339925173667</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.004756814537680365</v>
+        <v>-0.00293960448957773</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.005825761624799563</v>
+        <v>-0.006199893105291255</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.003687867450561177</v>
+        <v>-0.0004275788348476195</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.001611940298507508</v>
+        <v>-0.00411544628540883</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.0004385964912280827</v>
+        <v>-0.0001068947087119021</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.00417910447761195</v>
+        <v>-0.004238805970149251</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.01677611940298509</v>
+        <v>-0.00573134328358208</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.0006860158311346231</v>
+        <v>-0.0007482629609833702</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.0006413682522715347</v>
+        <v>-0.0001194029850746237</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.003367183324425427</v>
+        <v>-0.001496525921966829</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.00432923570283269</v>
+        <v>-0.002939604489577718</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.007856761090326025</v>
+        <v>-0.01127739176910737</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.0002409638554216831</v>
+        <v>-0.0001194029850746237</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.002030999465526417</v>
+        <v>-0.010712401055409</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.004382683057188664</v>
+        <v>-0.0007482629609833813</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.005751978891820631</v>
+        <v>-0.009182058047493447</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.003848209513629075</v>
+        <v>-0.008284339925173734</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0001603420630678864</v>
+        <v>-0.000261643118785948</v>
       </c>
       <c r="BD5" t="n">
-        <v>-9.823182711197199e-05</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.00256716417910452</v>
+        <v>-0.002585751978891859</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.006146445750935314</v>
+        <v>-0.01868073878627972</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.0008895866038722722</v>
+        <v>-0.001213720316622757</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.004275788348476739</v>
+        <v>-0.0002137894174237931</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.001282736504543003</v>
+        <v>-0.002058047493403736</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.008605024051309418</v>
+        <v>-0.006306787814003146</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.002832709780865817</v>
+        <v>-0.0009620523784072188</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.0002672367717798108</v>
+        <v>-0.0005232862375719183</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.004756814537680376</v>
+        <v>-0.004275788348476706</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.003007915567282371</v>
+        <v>-0.004802110817941962</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.00161194029850753</v>
+        <v>-0.001846965699208503</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.01368252271512561</v>
+        <v>-0.0007482629609834812</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.006787814003206827</v>
+        <v>-0.01223944414751474</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.001710315339390678</v>
+        <v>-0.001084337349397546</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.001031434184675783</v>
+        <v>-0.0009620523784072077</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.01330839123463388</v>
+        <v>-0.006574024585783045</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.002298236237306239</v>
+        <v>-0.006360235168359207</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-17</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.008711918760021364</v>
+        <v>-0.009139497594869105</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.004489577765900588</v>
+        <v>-0.002565473009086017</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.003046499198289687</v>
+        <v>-0.006306787814003167</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.003164179104477638</v>
+        <v>-0.0005373134328358065</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.007696419027258139</v>
+        <v>-0.004970603955104247</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.005772314270443601</v>
+        <v>-0.000994243851386667</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.003794762159273102</v>
+        <v>-0.002598120508568358</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.003271767810026427</v>
+        <v>-0.008601583113456501</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.001936159079016164</v>
+        <v>-0.0007228915662650159</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.00689470871191874</v>
+        <v>-0.008498129342597582</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.0007915567282322566</v>
+        <v>-0.0001583113456464336</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.004917156600748251</v>
+        <v>-0.01015499732763232</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-5.344735435596215e-05</v>
+        <v>-5.344735435595105e-05</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.0008358208955224211</v>
+        <v>-0.001084337349397557</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.00162650602409643</v>
+        <v>-0.0007326007326006967</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.001480263157894779</v>
+        <v>-0.0001055408970976224</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.001260964912280738</v>
+        <v>-0.0001046572475143725</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.001260964912280738</v>
+        <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.0001068947087119243</v>
+        <v>-0.0004186289900575235</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.002192982456140413</v>
+        <v>-0.000963855421686699</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.004275788348476727</v>
+        <v>-0.000361445783132508</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.003046499198289665</v>
+        <v>-0.005184393372528106</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.00630678781400319</v>
+        <v>-0.003848209513629097</v>
       </c>
       <c r="CU5" t="n">
-        <v>-4.911591355598599e-05</v>
+        <v>-0.00101549973276317</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0.000694815606627397</v>
       </c>
       <c r="CW5" t="n">
         <v>0</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0.006092998396579364</v>
+        <v>-0.001674515960230227</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.008658471405665391</v>
+        <v>-0.002093144950287762</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-5.527915975677145e-05</v>
+        <v>0</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0.0001068947087119243</v>
+        <v>-0.0001068947087119354</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0.001656867985034716</v>
+        <v>-0.0002388059701492473</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0.002407116692830924</v>
+        <v>-0.00104657247514387</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0.001443078567610889</v>
+        <v>-0.0003206841261357729</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0.001425438596491268</v>
+        <v>-0.000662650602409609</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.001936159079016186</v>
+        <v>-0.0005804749340369564</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0.0005482456140351033</v>
+        <v>-0.001098901098901073</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.01416354890432923</v>
+        <v>-0.01223944414751474</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.0007164179104477752</v>
+        <v>-0.0006948156066274302</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.0008349705304518396</v>
+        <v>-0.0001569858712715422</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0.003343283582089573</v>
+        <v>-0.0005804749340369674</v>
       </c>
       <c r="DL5" t="n">
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0.001134328358208969</v>
+        <v>-0.0002093144950287562</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.005505077498663802</v>
+        <v>-0.004578313253012001</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.005602409638554217</v>
+        <v>-0.005451630144307895</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.01228915662650605</v>
+        <v>-0.002084446819882457</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0</v>
+        <v>-0.0005344735435595215</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.0008017103153393768</v>
+        <v>0</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.0006802721088434938</v>
+        <v>-0.002405130946018208</v>
       </c>
       <c r="DT5" t="n">
+        <v>-0.001686746987951793</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>-0.01047568145376808</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>-0.0004709576138147376</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>-0.00100263852242749</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>-0.01427710843373491</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>-0.0001583113456464336</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>-0.001674515960230216</v>
+      </c>
+      <c r="EB5" t="n">
         <v>-0.006204819277108409</v>
       </c>
-      <c r="DU5" t="n">
-        <v>-0.005237840726884014</v>
-      </c>
-      <c r="DV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW5" t="n">
-        <v>-0.0002192982456140413</v>
-      </c>
-      <c r="DX5" t="n">
-        <v>-0.0008349705304518396</v>
-      </c>
-      <c r="DY5" t="n">
-        <v>-0.009299839657936937</v>
-      </c>
-      <c r="DZ5" t="n">
-        <v>-5.344735435596215e-05</v>
-      </c>
-      <c r="EA5" t="n">
-        <v>-0.001517530088958585</v>
-      </c>
-      <c r="EB5" t="n">
-        <v>-0.006268656716417964</v>
-      </c>
       <c r="EC5" t="n">
-        <v>-0.001809210526315841</v>
+        <v>-0.000361445783132508</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0.0005482456140351033</v>
+        <v>-0.0004179104477611828</v>
       </c>
       <c r="EE5" t="n">
         <v>0</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0.001194029850746314</v>
+        <v>-0.000662650602409598</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.002746268656716455</v>
+        <v>-0.001175841795831156</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0.0003869541182974001</v>
+        <v>-0.0002137894174238819</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.0007186290768380288</v>
+        <v>-0.0008551576696953833</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.001791044776119455</v>
+        <v>-0.0007915567282322123</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.002865671641791079</v>
+        <v>-0.0003166226912928672</v>
       </c>
       <c r="EL5" t="n">
         <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0.0001658374792703143</v>
+        <v>-5.232862375719183e-05</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0.0004275788348476306</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.0001096491228070207</v>
+        <v>-0.001068947087119243</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.001970149253731401</v>
+        <v>-0.0008017103153393323</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.0001068947087119243</v>
+        <v>0</v>
       </c>
       <c r="ES5" t="n">
         <v>0</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.002029850746268713</v>
+        <v>-0.000474934036939334</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.0004911591355598599</v>
+        <v>-0.001336183858898998</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0.0001055408970976446</v>
+        <v>0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.004649919828968452</v>
+        <v>-0.003260288615713558</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.001977552111170467</v>
+        <v>-0.0001569858712715755</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.0002763957987838572</v>
+        <v>-0.0004275788348476972</v>
       </c>
     </row>
     <row r="6">
@@ -3083,376 +3083,376 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.0007977463907285238</v>
+        <v>-0.0002686567164179032</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.000328947368421062</v>
+        <v>-0.0001355421686746905</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.000706752382664999</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0002655992888350806</v>
+        <v>-0.0001658374792703144</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.001555224944225947</v>
+        <v>-0.000361445783132508</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0005991549695836873</v>
+        <v>-0.00019416471857579</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0009718076285240739</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0001534757450856128</v>
+        <v>-3.957783641160839e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.0001488539911625342</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0001202565473009148</v>
+        <v>-0.0003162650602409445</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0006508486590793006</v>
+        <v>1.492537313432796e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0001957831325301584</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0005992127714839507</v>
+        <v>-0.0003125437071669596</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0002599202781274262</v>
+        <v>0.0001044776119402874</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.001671023046289524</v>
+        <v>-0.0001464208591794802</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001790955570809771</v>
+        <v>-0.0005413594677216027</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0002072968490878929</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0002631183867857489</v>
+        <v>-0.0002374670184696504</v>
       </c>
       <c r="V6" t="n">
-        <v>-4.008551576695496e-05</v>
+        <v>-0.0003162650602409444</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0008570388303606625</v>
+        <v>-0.0002849041272885738</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0008790523893390051</v>
+        <v>2.4557956777993e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.0003731343283582072</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0007582686077760997</v>
+        <v>-0.0006861443716745298</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0004414483527920565</v>
+        <v>-0.000144124627728065</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0001243781094527357</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.0005189656729378516</v>
+        <v>2.4557956777993e-05</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0004156468430310284</v>
+        <v>0.0001438859563992728</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.003236328398169774</v>
+        <v>0.001043665329379645</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.0009813675845488895</v>
+        <v>-0.0005120481927710529</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0007253763252152018</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
+        <v>5.176230830131746e-05</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.0001355421686746905</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-9.197355288612095e-06</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.005857932559425075</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-8.326672684688675e-18</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>4.658267696690531e-05</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>4.911591355598876e-05</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.001413558063935977</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.003013271993446437</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-4.51807228915635e-05</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0.000180722891566254</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-0.0001202565473009398</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-0.0004256291103847732</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.0002221822613838159</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-0.0001881620919150895</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0.0004159153986335761</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-0.001102218901993204</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-0.0003045760209939213</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-0.0008507462686566936</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.0002405130946018297</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-0.0001841846758349807</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0.0001791044776119355</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-0.0002837169573817577</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-8.955223880596774e-05</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-0.0001382806362922262</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-0.00010797756891196</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>-0.0001791044776119355</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-8.955223880596774e-05</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0.000799989597321757</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-0.0005162602918269449</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>-0.0004191812710470421</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-0.0004659233950728037</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>-0.0001190648778285397</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.31926121372028e-05</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>-0.000160492670087542</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>-0.0006022747707246535</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>-0.0001187335092348252</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>-0.0003340459647247163</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>-0.0002575906745953538</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>-0.0001485842555034811</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>-0.0001754467792615844</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>-0.000361445783132508</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>-0.000180722891566254</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>-9.0361445783127e-05</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>-0.000195648264700582</v>
+      </c>
+      <c r="CT6" t="n">
         <v>-4.477611940298387e-05</v>
       </c>
-      <c r="AI6" t="n">
-        <v>-0.0002590394596191259</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.0004268233797545123</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0.004451950281336384</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-0.0001944290319171649</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0.0006367238059667713</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>-0.0007078313253012086</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>-7.915567282325564e-05</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>-7.3673870333979e-05</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>-0.0008654429991377082</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0.0009227648427303919</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-0.000205118182470837</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>-4.111842105263275e-05</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>-0.0001202565473009148</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>-0.0006174698795180732</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>-0.0003162650602410028</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-0.0009261644139075959</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>-0.001086583382194364</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>-0.0001723791038417133</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>-0.0006070645536935925</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>-0.0001355421686747155</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>-0.003153960289413449</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>-0.0003125437071670095</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>0.0004427860696517349</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>-0.002927535255606295</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>-0.0002535431943362449</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>-8.017103153394324e-05</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>-0.001441371443158346</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>9.673852957433338e-05</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>-0.0004066265060241464</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>-0.001020408163265249</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>-0.000492537313432856</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>-0.0001300183818426448</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>-0.000234020526265874</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>-0.0005218109695721285</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>-8.955223880596774e-05</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>-0.001209411904402019</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>-0.002065017949076606</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>-0.0003333690589176236</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>8.291873963515717e-05</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>-0.001033131048056377</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>-0.0001981042923242082</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>-0.001180857759395829</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>-0.0005454152575687654</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>-0.001108895306175586</v>
-      </c>
-      <c r="CG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>-0.0007876718806150345</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL6" t="n">
-        <v>-0.0005621790535626114</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>-9.036144578314365e-05</v>
-      </c>
-      <c r="CN6" t="n">
+      <c r="CU6" t="n">
+        <v>-3.924646781789388e-05</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>-0.0001343283582089516</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>-0.0003106621737609894</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>-0.0001492483090255597</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-0.000180722891566254</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>-7.915567282321679e-05</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>-0.0005263403377847531</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0.0004247312294588801</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>-0.0008083653876720664</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>-0.0007404008978852377</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>-0.000526029491098695</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>-3.924646781789388e-05</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>-7.849293563578775e-05</v>
+      </c>
+      <c r="DT6" t="n">
         <v>-4.477611940298387e-05</v>
       </c>
-      <c r="CO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>-0.0002710843373493893</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>-0.0007393670869215302</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>-0.0004010236195441968</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>-0.001031509121061355</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>-0.0004477449270767625</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>-0.00212711950451821</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB6" t="n">
-        <v>-7.915567282323343e-05</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>-0.0006528793765007285</v>
-      </c>
-      <c r="DD6" t="n">
-        <v>-3.924646781789388e-05</v>
-      </c>
-      <c r="DE6" t="n">
-        <v>-0.0002662023338935255</v>
-      </c>
-      <c r="DF6" t="n">
-        <v>-0.001495854063018267</v>
-      </c>
-      <c r="DG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH6" t="n">
-        <v>-0.001170438332276505</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>-9.261696742251247e-05</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>-0.0006202113451580143</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>-0.0001177394034536733</v>
-      </c>
-      <c r="DL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM6" t="n">
-        <v>-8.291873963515718e-05</v>
-      </c>
-      <c r="DN6" t="n">
-        <v>-0.001262426917887624</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>-0.001700221769768939</v>
-      </c>
-      <c r="DP6" t="n">
-        <v>-0.001157000763782864</v>
-      </c>
-      <c r="DQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS6" t="n">
-        <v>-3.68369351669895e-05</v>
-      </c>
-      <c r="DT6" t="n">
-        <v>-0.0006954792855633357</v>
-      </c>
       <c r="DU6" t="n">
-        <v>-0.001069940534793121</v>
+        <v>-0.0006611670562848143</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
@@ -3461,10 +3461,10 @@
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.0004376454010705105</v>
+        <v>-0.0003540572583101143</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0.001367514835461289</v>
+        <v>-0.001720174859973195</v>
       </c>
       <c r="DZ6" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.001196496512365291</v>
+        <v>-0.001195108793382449</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0.0003512553688833742</v>
+        <v>2.498001805406602e-17</v>
       </c>
       <c r="ED6" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
         <v>0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.0004282674383714463</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.0002773500297688192</v>
+        <v>-0.0003562005277045005</v>
       </c>
       <c r="EH6" t="n">
         <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.0001978891820580836</v>
+        <v>-0.0004541332855738266</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0</v>
+        <v>-0.000180722891566254</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.0005446323552786903</v>
+        <v>0</v>
       </c>
       <c r="EL6" t="n">
         <v>0</v>
@@ -3518,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0.0007228915662650577</v>
+        <v>0</v>
       </c>
       <c r="ER6" t="n">
         <v>0</v>
@@ -3527,22 +3527,22 @@
         <v>0</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.0003915662650602391</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0.0003372858187367184</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0.0008933788273215671</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>-4.518072289157182e-05</v>
+        <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-4.008551576697162e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3552,220 +3552,220 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0004648554355166645</v>
+        <v>0.0001075833122356706</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>8.539964168448045e-05</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.616431187858481e-05</v>
+        <v>0.0001773874999351943</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.741228070175517e-05</v>
+        <v>0.0002536113432829778</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0002956422941274128</v>
+        <v>7.983711653476445e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.783645360880164e-05</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0006084915568003169</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5.232862375720293e-05</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-9.823182711196643e-05</v>
+        <v>0.0003717854148147182</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0005128163395597852</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0002166873638089151</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.002259666708503166</v>
+        <v>0.001576140210226218</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.0006140922529167369</v>
+        <v>-7.923639548370608e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0007288998595389728</v>
+        <v>-0.0001324279144935714</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>8.291873963515717e-05</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0003469880460174657</v>
+        <v>2.4557956777993e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0002054269710420553</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001705698481277779</v>
+        <v>0.0005364849747159727</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>-2.130328780741155e-05</v>
+        <v>0.000164473684210531</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0003581780425358616</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.527915975678255e-05</v>
+        <v>0.0002197528439673024</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0008899944720840103</v>
+        <v>0.002867439120188509</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.01028790766722289</v>
+        <v>0.006162804459488263</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.0003280706322342231</v>
+        <v>-0.0001096491228070207</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.0001381978993919286</v>
+        <v>6.02409638554291e-05</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0002114202470988036</v>
+        <v>0.0002476197230223187</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.0001155201236122005</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.00321248194979698</v>
+        <v>0.0004502783504505059</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.01009811236330898</v>
+        <v>0.01241836909248303</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0002690685771806034</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.001401663102615558</v>
+        <v>0.00116795540370439</v>
       </c>
       <c r="AN7" t="n">
-        <v>-5.527915975677145e-05</v>
+        <v>2.4557956777993e-05</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0008280509004684189</v>
+        <v>0.0005061237348875536</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.000261160729152099</v>
+        <v>8.291873963515717e-05</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-7.881721991966351e-05</v>
+        <v>3.012048192771455e-05</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.006932552365872013</v>
+        <v>0.005363709636794107</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>0.000131926121372028</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.0002686567164179032</v>
+        <v>5.379750497616076e-05</v>
       </c>
       <c r="AU7" t="n">
         <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.638522427438339e-05</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0003259088987529024</v>
+        <v>3.012048192771455e-05</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>-5.698629488483655e-05</v>
+        <v>-5.970149253731183e-05</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-2.4557956777993e-05</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0005063571033720072</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0003467431732205595</v>
+        <v>-3.026660462551733e-05</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.985074626865591e-05</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0001838129203376171</v>
+        <v>-3.0120481927709e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.0005249619616390754</v>
+        <v>0.0004682817636961434</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.665334536937735e-17</v>
+        <v>0</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.0003239358761746747</v>
+        <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.001640213007961966</v>
+        <v>0.0007987642714095744</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.0005532937249982273</v>
+        <v>0.0001018863621048027</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0006116646319851759</v>
+        <v>5.970149253731183e-05</v>
       </c>
       <c r="BL7" t="n">
         <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0003123678926231499</v>
+        <v>0</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.001272571328035649</v>
+        <v>0.0001093568774114151</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.000107607783513991</v>
+        <v>0.0001503326739795252</v>
       </c>
       <c r="BP7" t="n">
-        <v>7.652819425775781e-05</v>
+        <v>0</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0003305384626574759</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>3.0120481927709e-05</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
         <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.0001404119953893612</v>
+        <v>0</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3774,73 +3774,73 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-2.985074626865591e-05</v>
+        <v>-0.000120481927710836</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.001115932943852754</v>
+        <v>0.0002213439382037163</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0001918859649122751</v>
+        <v>0.0003211594287892361</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.0005516596734086498</v>
+        <v>8.5399641684486e-05</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0.000353151292218229</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-2.697356590641839e-07</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>5.482456140352699e-05</v>
       </c>
       <c r="CE7" t="n">
         <v>0</v>
       </c>
       <c r="CF7" t="n">
-        <v>-3.012048192771455e-05</v>
+        <v>0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0003721813330205603</v>
+        <v>0</v>
       </c>
       <c r="CH7" t="n">
-        <v>8.46753076721607e-05</v>
+        <v>8.154823858149141e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>-1.668757544914245e-05</v>
+        <v>0</v>
       </c>
       <c r="CJ7" t="n">
         <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>9.036144578312699e-05</v>
+        <v>-8.017103153396544e-05</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0001791044776119355</v>
+        <v>0</v>
       </c>
       <c r="CM7" t="n">
-        <v>9.98381822125971e-05</v>
+        <v>0</v>
       </c>
       <c r="CN7" t="n">
         <v>0</v>
       </c>
       <c r="CO7" t="n">
-        <v>8.642516971528736e-05</v>
+        <v>0</v>
       </c>
       <c r="CP7" t="n">
         <v>0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>5.970149253731183e-05</v>
+        <v>0</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.0001386681523619648</v>
+        <v>0</v>
       </c>
       <c r="CS7" t="n">
-        <v>7.675549343438281e-05</v>
+        <v>0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0.0003150760938491037</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
         <v>0</v>
@@ -3852,10 +3852,10 @@
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>-1.110223024625157e-17</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>-0.001355421686746999</v>
+        <v>-2.763957987838572e-05</v>
       </c>
       <c r="CZ7" t="n">
         <v>0</v>
@@ -3867,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>-4.940815895160267e-05</v>
+        <v>0</v>
       </c>
       <c r="DD7" t="n">
         <v>0</v>
@@ -3876,19 +3876,19 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.0003654194614871598</v>
+        <v>0</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.0001096424168131382</v>
+        <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.0001896900565932724</v>
+        <v>-0.0003614457831325024</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0005503686187376788</v>
+        <v>-9.036144578312699e-05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>-0.000316961144196487</v>
+        <v>0</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
@@ -3900,13 +3900,13 @@
         <v>0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0.0002897956422268533</v>
+        <v>-0.0002040782927467899</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.0006084865778905269</v>
+        <v>-0.0001260444528605575</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0.0006486126225908439</v>
+        <v>-0.000137407923861288</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
@@ -3918,10 +3918,10 @@
         <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.0007728026533996568</v>
+        <v>5.344735435596215e-05</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0.0008926443608026969</v>
+        <v>-0.0003506129782286926</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0.0009188045264396705</v>
+        <v>-8.244910568487307e-05</v>
       </c>
       <c r="DZ7" t="n">
         <v>0</v>
@@ -3942,10 +3942,10 @@
         <v>0</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.0003347565816410381</v>
+        <v>-0.0002374670184696559</v>
       </c>
       <c r="EC7" t="n">
-        <v>-0.0001569858712715755</v>
+        <v>0.0002733141756834645</v>
       </c>
       <c r="ED7" t="n">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-5.277044854882784e-05</v>
+        <v>0</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
@@ -3999,13 +3999,13 @@
         <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0.0001313809246923647</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0.0003401360544217469</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
         <v>0</v>
@@ -4021,403 +4021,403 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002082531421838132</v>
+        <v>0.0007016290701779115</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000755793453895659</v>
+        <v>0.0001149194025611394</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0002467105263158021</v>
+        <v>0.0009966316343317182</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0001033720287451606</v>
+        <v>8.291873963516828e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000810330141560145</v>
+        <v>0.002671785380952032</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003107190922964937</v>
+        <v>0.0002051181824708703</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0005829732914375523</v>
+        <v>0.000164473684210531</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0003162650602409889</v>
+        <v>0.0002154878197986737</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002072968490878957</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001169645195077229</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5.152544620691535e-05</v>
+        <v>4.145936981757859e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0009623737235677833</v>
+        <v>0.0005465198195478138</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0009835906808188162</v>
+        <v>0.0004593969545729409</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0008059078666066755</v>
+        <v>0.0001828693024244266</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005201574544858169</v>
+        <v>0.002169463353322296</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.0002569968634749869</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001995738108052506</v>
+        <v>0.0006743638036383671</v>
       </c>
       <c r="T8" t="n">
-        <v>5.420057699193348e-05</v>
+        <v>0.000563797144752226</v>
       </c>
       <c r="U8" t="n">
+        <v>0.0004029051529501531</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.0002110182021618834</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.0003051565671467943</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.001240717038453962</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.957783641160839e-05</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.0005048583331361073</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.0001473477406679663</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.00116413224302353</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.008009725469040361</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.02202857482561828</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.001038867218144887</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.00124977461959011</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.001878486205619562</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.003627321619454796</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.0273512889864009</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.0006439761770252379</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.007601110542275396</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.0004449037581341103</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.003829973284860524</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.0005335880276396698</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.0003081054182607818</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.01585021005072926</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.001777788955428819</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.0002888417346724459</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.0006247738082928445</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.0004759885901207711</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>8.017103153392657e-05</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0.0002710843373494226</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.0002259036144578675</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0.0004212271973465965</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.0004444444444444418</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>9.036144578314365e-05</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.0001569858712716088</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>3.683693516698116e-05</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0.001703972490711081</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0.0001658374792703144</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0.0002581301459134711</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0.004288494243851399</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.001085856584231693</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.0003293734786384589</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.0004293003436570908</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0.001420799283368984</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0.0004581843127069246</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.000380925089991202</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>4.111842105263275e-05</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0.0003299845298818576</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>4.145936981757859e-05</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0.0007630122473653384</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0.0007411544252422187</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0.001516752437944852</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>7.915567282321679e-05</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>3.957783641160839e-05</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0.0008685195082843183</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>4.518072289157182e-05</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.0002242852005035073</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.0003329272341259571</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0.0003048457566530244</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0.0001945426815054968</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0.0005240499504952867</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0.0003289272504393981</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0.0003577244300585647</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>2.498001805406602e-17</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0.0003667421910920121</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0.0001105108055009685</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>9.036144578314365e-05</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0.001310240963855458</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0.0002576272310344768</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>7.915567282321955e-05</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0.0001466417715753288</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0.0003817311902589105</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>9.4515820494262e-05</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0.0004145936981757858</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0.0002206586876768696</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0.0006012827365045159</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
         <v>8.017103153394324e-05</v>
       </c>
-      <c r="V8" t="n">
-        <v>0.001353792478621602</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.002937390443500179</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.001377588749305353</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.00124999999999999</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.000696379141172801</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0.01083971936463803</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.02295921258524212</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.0002956588513326475</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.0004983698945165316</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.0008977005778711799</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.0007053586072775758</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.004860769609048404</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0.02836441636371151</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0.001311936360414251</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.006496715793091037</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0.0004409406734366627</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.003812420389041271</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0.0004057811207813067</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0.0004737910384169458</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0.01718007192288104</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0.0005338248869742213</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0.001156791344482405</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0.001172425852596462</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.0003823947227770241</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.0009328467600432239</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0.0002824765063570961</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0.0005560892554496266</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.0001634407789248699</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0.001300813847806334</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0.002030668114107789</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0.0001654965305053685</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0.0001343283582089544</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0.003103111198627226</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0.001862515852885191</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0.0001711652933759494</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>0.0007727866942881662</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>0.002367908177727215</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.0008269183484330006</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.001203911744537647</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.0004749340369392923</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>0.002618151178654793</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>0.001472082870434632</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>0.0005260294910987202</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>0.0005327812790416997</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>0.001064747115109488</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>0.0009219668626403139</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>0.001242159653751762</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>0.0016152704485488</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>0.0003222255777728139</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>0.0008915055330208782</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>0.003084577114427842</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>0.001704197871121041</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>0.0001233552631578983</v>
-      </c>
-      <c r="CC8" t="n">
-        <v>0.0002654814508694231</v>
-      </c>
-      <c r="CD8" t="n">
-        <v>0.0008666580173146754</v>
-      </c>
-      <c r="CE8" t="n">
-        <v>0.0005237116289852212</v>
-      </c>
-      <c r="CF8" t="n">
+      <c r="DO8" t="n">
+        <v>0.0004557121192284186</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0.0004232500501157283</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0.001127059528813029</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0.0004145936981757858</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
         <v>4.145936981757859e-05</v>
       </c>
-      <c r="CG8" t="n">
-        <v>0.0009929102812576917</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>0.0006855753301903134</v>
-      </c>
-      <c r="CI8" t="n">
-        <v>0.000290689789959872</v>
-      </c>
-      <c r="CJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK8" t="n">
-        <v>0.0006813908394423223</v>
-      </c>
-      <c r="CL8" t="n">
-        <v>0.0007535019298866464</v>
-      </c>
-      <c r="CM8" t="n">
-        <v>0.0003700700456488265</v>
-      </c>
-      <c r="CN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>0.0001871063531993206</v>
-      </c>
-      <c r="CP8" t="n">
-        <v>3.683693516699782e-05</v>
-      </c>
-      <c r="CQ8" t="n">
-        <v>0.0003548963062592503</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>0.001119385192484951</v>
-      </c>
-      <c r="CS8" t="n">
-        <v>0.001181166535742331</v>
-      </c>
-      <c r="CT8" t="n">
-        <v>-1.50602409638545e-05</v>
-      </c>
-      <c r="CU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX8" t="n">
-        <v>0.0005115087214529802</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>-0.0005922860829514847</v>
-      </c>
-      <c r="CZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>0.0002974363825805876</v>
-      </c>
-      <c r="DD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE8" t="n">
-        <v>0.0006438224675225978</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>-0.0002035262946918332</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>0.0004782862794461329</v>
-      </c>
-      <c r="DH8" t="n">
-        <v>0.0009425009958059032</v>
-      </c>
-      <c r="DI8" t="n">
-        <v>0.001647749180643959</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>4.145936981757859e-05</v>
-      </c>
-      <c r="DK8" t="n">
-        <v>0.0001202565473009065</v>
-      </c>
-      <c r="DL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>0.0001469802244788959</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>0.0007067044232515168</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>0.0002902155887230418</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>0.002247290615249481</v>
-      </c>
-      <c r="DQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT8" t="n">
-        <v>0.001552913405835543</v>
-      </c>
-      <c r="DU8" t="n">
-        <v>7.685052145951218e-05</v>
-      </c>
-      <c r="DV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX8" t="n">
-        <v>4.477611940298387e-05</v>
-      </c>
-      <c r="DY8" t="n">
-        <v>0.000858304420878056</v>
-      </c>
-      <c r="DZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA8" t="n">
-        <v>0</v>
-      </c>
       <c r="EB8" t="n">
-        <v>0.00225189812072589</v>
+        <v>0.0003724524308283128</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.001061359867329992</v>
+        <v>0.0007598696064583937</v>
       </c>
       <c r="ED8" t="n">
-        <v>0</v>
+        <v>0.0001807228915662873</v>
       </c>
       <c r="EE8" t="n">
         <v>0</v>
@@ -4426,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>3.924646781792717e-05</v>
+        <v>0</v>
       </c>
       <c r="EH8" t="n">
         <v>0</v>
@@ -4435,16 +4435,16 @@
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>4.145936981757859e-05</v>
+        <v>0</v>
       </c>
       <c r="EK8" t="n">
-        <v>4.51807228915635e-05</v>
+        <v>0</v>
       </c>
       <c r="EL8" t="n">
         <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>7.84929356358044e-05</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
         <v>0</v>
@@ -4456,7 +4456,7 @@
         <v>0</v>
       </c>
       <c r="EQ8" t="n">
-        <v>3.683693516699782e-05</v>
+        <v>0</v>
       </c>
       <c r="ER8" t="n">
         <v>0</v>
@@ -4465,22 +4465,22 @@
         <v>0</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0001333387032402156</v>
+        <v>0</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0002487562189054715</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>7.915567282320847e-05</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0001177394034537066</v>
+        <v>0</v>
       </c>
       <c r="EY8" t="n">
-        <v>4.51807228915635e-05</v>
+        <v>3.957783641160839e-05</v>
       </c>
     </row>
     <row r="9">
@@ -4490,443 +4490,443 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007951807228915687</v>
+        <v>0.001883830455259072</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001656867985034749</v>
+        <v>0.003474078033137318</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003035060177917381</v>
+        <v>0.0009419152276295528</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001635883905013147</v>
+        <v>0.003794762159273091</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0003166226912928672</v>
+        <v>0.0003741314804916685</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0103012048192771</v>
+        <v>0.01439759036144582</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003124999999999989</v>
+        <v>0.00855421686746991</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002005277044854825</v>
+        <v>0.001779173207744689</v>
       </c>
       <c r="J9" t="n">
-        <v>0.005756578947368396</v>
+        <v>0.00282574568288857</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001144578313253031</v>
+        <v>0.0009942438513867446</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0007228915662650492</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001253731343283548</v>
+        <v>0.002832709780865894</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005361445783132524</v>
+        <v>0.004337349397590395</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004061998931052913</v>
+        <v>0.00267236771779793</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003433734939759037</v>
+        <v>0.002197802197802268</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01120481927710842</v>
+        <v>0.004698795180722959</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002409638554216875</v>
+        <v>0.006039551042223379</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003734939759036138</v>
+        <v>0.002349397590361491</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002902374670184615</v>
+        <v>0.00181721004810258</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001746987951807233</v>
+        <v>0.004596472474612467</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003087388801674562</v>
+        <v>0.0006413682522715347</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001977552111170511</v>
+        <v>0.003349031920460532</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004133961276818476</v>
+        <v>0.002093144950287862</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.482456140351033e-05</v>
+        <v>0.002084446819882457</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.006626506024096379</v>
+        <v>0.002469879518072338</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.001831501831501881</v>
+        <v>0.0007127192982456342</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0007831325301204783</v>
+        <v>0.002512025654730043</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01156626506024098</v>
+        <v>0.01222891566265064</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.03180722891566264</v>
+        <v>0.01688936397648311</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.02719298245614032</v>
+        <v>0.02612137203166224</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.006121372031662209</v>
+        <v>0.006015831134564597</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.004518072289156605</v>
+        <v>0.004036144578313283</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.002886157135221834</v>
+        <v>0.002565473009086017</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.002409638554216853</v>
+        <v>0.003580972741849309</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.01335092348284955</v>
+        <v>0.007387862796833744</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.03361445783132531</v>
+        <v>0.04035275253874929</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001883830455259072</v>
+        <v>0.00421686746987956</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.04096385542168673</v>
+        <v>0.03066265060240968</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.003905013192612084</v>
+        <v>0.005481927710843415</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.0105421686746988</v>
+        <v>0.006506024096385588</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.002137894174238386</v>
+        <v>0.001763762693746629</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.001589912280701722</v>
+        <v>0.002168674698795214</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.02822020309994655</v>
+        <v>0.03554249064671294</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.002521929824561364</v>
+        <v>0.006360235168359129</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.00664573521716384</v>
+        <v>0.002618920363441968</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.002831325301204812</v>
+        <v>0.001496525921966818</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.00308738880167454</v>
+        <v>0.00230245944531664</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.009837781266352753</v>
+        <v>0.006746987951807259</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001443078567610911</v>
+        <v>0.0006279434850864129</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.001492537313432796</v>
+        <v>0.003153393907001567</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.001899736147757203</v>
+        <v>0.002137894174238342</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.008493975903614458</v>
+        <v>0.008215593929879705</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.01042168674698796</v>
+        <v>0.01130298273155419</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001686746987951804</v>
+        <v>0.0009620523784072077</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0004810261892036483</v>
+        <v>0.001817210048102591</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.01259036144578314</v>
+        <v>0.002405130946018119</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.007587650444793348</v>
+        <v>0.009578313253012094</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.0005421686746987619</v>
+        <v>0.003715332286760886</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.002289156626506039</v>
+        <v>0.0008372579801151691</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.02042168674698796</v>
+        <v>0.006520577231427005</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.002741228070175405</v>
+        <v>0.006488749345892253</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.003673245614035081</v>
+        <v>0.001927710843373531</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001517530088958707</v>
+        <v>0.001282736504542981</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.01650602409638556</v>
+        <v>0.01427710843373498</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.006024096385542177</v>
+        <v>0.009419152276295162</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.001817210048102635</v>
+        <v>0.0008372579801151691</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.001924104756814526</v>
+        <v>0.002930402930402976</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.001807228915662651</v>
+        <v>0.002354788069073821</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.001549973276322791</v>
+        <v>0.0005421686746988396</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.007590361445783123</v>
+        <v>0.0004810261892035816</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.001719056974459776</v>
+        <v>0.0002638522427440559</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.003046499198289665</v>
+        <v>0.001867469879518113</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0001068947087119243</v>
+        <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0006948156066274747</v>
+        <v>0.0004420432220038961</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.00915662650602409</v>
+        <v>0.01111704970603951</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.01289156626506025</v>
+        <v>0.01084337349397595</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.002796052631578916</v>
+        <v>0.004115446285408908</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.001635883905013147</v>
+        <v>0.0006876227897838593</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.002725815072153914</v>
+        <v>0.006306787814003156</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.009457831325301213</v>
+        <v>0.005722891566265098</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.001864035087719273</v>
+        <v>0.002197802197802246</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0007915567282321568</v>
+        <v>0.006253340459647194</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.002672367717797985</v>
+        <v>0.0006413682522715347</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.003527525387493324</v>
+        <v>0.001445783132530154</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.001266490765171469</v>
+        <v>0.004222340994120832</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0</v>
+        <v>0.0001603420630678642</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.00336718332442546</v>
+        <v>0.001068947087119232</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.002773417059131389</v>
+        <v>0.004008551576696995</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.001336183858898998</v>
+        <v>0.0005756148613291767</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0009498680738786013</v>
+        <v>0.002137894174238408</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.001213720316622657</v>
+        <v>0.0007482629609833702</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0001583113456464336</v>
+        <v>0.0001068947087119021</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0007387862796833566</v>
+        <v>0.0004709576138148264</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.002686403508771895</v>
+        <v>0.01004810261892032</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.005184393372528029</v>
+        <v>0.005128205128205165</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.0005804749340369231</v>
+        <v>0.0004709576138147931</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0001068947087119243</v>
+        <v>0.000587920897915506</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0004810261892036594</v>
+        <v>0</v>
       </c>
       <c r="CW9" t="n">
         <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.003087388801674573</v>
+        <v>0.009887760555852432</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0002672367717798108</v>
+        <v>0.001977552111170455</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0004749340369393007</v>
+        <v>0</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0001791044776119244</v>
+        <v>0.0002763957987838572</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0003206841261357729</v>
+        <v>0.001175841795831067</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.001496525921966829</v>
+        <v>0.0009086050240512678</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0006948156066274747</v>
+        <v>0.0008372579801151691</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.00114457831325302</v>
+        <v>0.0009086050240512455</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.002458578300374126</v>
+        <v>0.001674515960230283</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.00251202565473011</v>
+        <v>0.001445783132530165</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.001389631213254927</v>
+        <v>0.002084446819882457</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.001987951807228905</v>
+        <v>0.0009942438513867668</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0002672367717798108</v>
+        <v>0.0004275788348476195</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.001336183858898987</v>
+        <v>0.002618920363442057</v>
       </c>
       <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0.003741314804917117</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.003634420096205193</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0.004275788348476783</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0.002084446819882446</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0.0006802721088435826</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>6.02409638554291e-05</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.004168893639764859</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0.002779262426509932</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0.0001068947087119021</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>6.02409638554513e-05</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0.000587920897915617</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.0001807228915662873</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.001122394441475105</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0.003741314804917217</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0.004810261892036293</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0.0004810261892036705</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>0.001360544217687121</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0.001936159079016275</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.0003614457831325746</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.0002137894174238042</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>5.344735435595105e-05</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0.0001068947087119021</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ9" t="n">
         <v>5.277044854881119e-05</v>
       </c>
-      <c r="DM9" t="n">
-        <v>0.00225013082155946</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>0.001437258153676058</v>
-      </c>
-      <c r="DO9" t="n">
-        <v>0.003206841261357529</v>
-      </c>
-      <c r="DP9" t="n">
-        <v>0.003848209513629064</v>
-      </c>
-      <c r="DQ9" t="n">
-        <v>5.344735435596215e-05</v>
-      </c>
-      <c r="DR9" t="n">
-        <v>0.0001194029850746237</v>
-      </c>
-      <c r="DS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT9" t="n">
-        <v>0.007108498129342588</v>
-      </c>
-      <c r="DU9" t="n">
-        <v>0.005963855421686726</v>
-      </c>
-      <c r="DV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX9" t="n">
-        <v>0.0009638554216867323</v>
-      </c>
-      <c r="DY9" t="n">
-        <v>0.002993051843933714</v>
-      </c>
-      <c r="DZ9" t="n">
-        <v>5.482456140351033e-05</v>
-      </c>
-      <c r="EA9" t="n">
-        <v>0.0002137894174238375</v>
-      </c>
-      <c r="EB9" t="n">
-        <v>0.003687867450561177</v>
-      </c>
-      <c r="EC9" t="n">
-        <v>0.002005277044854825</v>
-      </c>
-      <c r="ED9" t="n">
-        <v>0.0004749340369393007</v>
-      </c>
-      <c r="EE9" t="n">
-        <v>0.0004275788348476861</v>
-      </c>
-      <c r="EF9" t="n">
-        <v>0.0007482629609834257</v>
-      </c>
-      <c r="EG9" t="n">
-        <v>0.0002137894174238486</v>
-      </c>
-      <c r="EH9" t="n">
-        <v>0.0014430785676109</v>
-      </c>
-      <c r="EI9" t="n">
-        <v>0.0007482629609834146</v>
-      </c>
-      <c r="EJ9" t="n">
-        <v>0.002244788882950277</v>
-      </c>
-      <c r="EK9" t="n">
-        <v>0.001977552111170489</v>
-      </c>
-      <c r="EL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EM9" t="n">
-        <v>0.0005344735435596105</v>
-      </c>
-      <c r="EN9" t="n">
-        <v>0.0006802721088435826</v>
-      </c>
-      <c r="EO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EP9" t="n">
-        <v>5.277044854881119e-05</v>
-      </c>
-      <c r="EQ9" t="n">
-        <v>0.0006802721088436048</v>
-      </c>
       <c r="ER9" t="n">
         <v>0</v>
       </c>
@@ -4934,22 +4934,22 @@
         <v>0</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.001603420630678776</v>
+        <v>0.0003206841261357174</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.002302631578947334</v>
+        <v>0.0006024096385542355</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.002773417059131411</v>
+        <v>0.001046572475143948</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.00186746987951808</v>
+        <v>0.001686746987951848</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.001325301204819274</v>
+        <v>0.0008017103153393435</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0003663003663004094</v>
+        <v>0.0002409638554217164</v>
       </c>
     </row>
   </sheetData>
